--- a/eduservices/SIM2_nav11.xlsx
+++ b/eduservices/SIM2_nav11.xlsx
@@ -1761,7 +1761,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="200">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="26" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2265,6 +2265,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="187" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="23" borderId="13" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="21" fillId="23" borderId="13" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="21" fillId="23" borderId="13" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="23" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="38" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9212,20 +9227,56 @@
   <sheetData>
     <row r="1" spans="3:62" ht="8" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="3:62" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G2" s="144" t="s">
-        <v>127</v>
-      </c>
+      <c r="C2" s="144" t="inlineStr">
+        <is>
+          <t>SIMULATION — OUVRIR OU FERMER UNE CLASSE</t>
+        </is>
+      </c>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
       <c r="H2" s="144"/>
       <c r="I2" s="144"/>
       <c r="J2" s="144"/>
       <c r="K2" s="144"/>
+      <c r="L2" s="144"/>
+      <c r="M2" s="144"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="144"/>
+      <c r="P2" s="144"/>
+      <c r="Q2" s="144"/>
+      <c r="R2" s="144"/>
+      <c r="S2" s="144"/>
+      <c r="T2" s="144"/>
+      <c r="U2" s="144"/>
+      <c r="V2" s="144"/>
     </row>
     <row r="3" spans="3:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C3" s="145" t="inlineStr">
+        <is>
+          <t>Budget 2027 · la décision se prend en colonne DÉCISION, tout le tableau suit</t>
+        </is>
+      </c>
+      <c r="D3" s="145"/>
+      <c r="E3" s="145"/>
+      <c r="F3" s="145"/>
       <c r="G3" s="145"/>
       <c r="H3" s="145"/>
       <c r="I3" s="145"/>
       <c r="J3" s="145"/>
       <c r="K3" s="145"/>
+      <c r="L3" s="145"/>
+      <c r="M3" s="145"/>
+      <c r="N3" s="145"/>
+      <c r="O3" s="145"/>
+      <c r="P3" s="145"/>
+      <c r="Q3" s="145"/>
+      <c r="R3" s="145"/>
+      <c r="S3" s="145"/>
+      <c r="T3" s="145"/>
+      <c r="U3" s="145"/>
+      <c r="V3" s="145"/>
     </row>
     <row r="4" spans="3:62" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="5" spans="3:62" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -9319,118 +9370,228 @@
       </c>
     </row>
     <row r="9" spans="3:62" ht="13.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C9" s="155"/>
+      <c r="C9" s="155" t="inlineStr">
+        <is>
+          <t>  CLASSES SIMULÉES</t>
+        </is>
+      </c>
       <c r="D9" s="156"/>
       <c r="E9" s="156"/>
       <c r="F9" s="157"/>
-      <c r="G9" s="155"/>
+      <c r="G9" s="155" t="inlineStr">
+        <is>
+          <t>  CLASSES FERMÉES</t>
+        </is>
+      </c>
       <c r="H9" s="157"/>
-      <c r="I9" s="155"/>
+      <c r="I9" s="155" t="inlineStr">
+        <is>
+          <t>  EFFECTIF PERDU</t>
+        </is>
+      </c>
       <c r="J9" s="157"/>
-      <c r="K9" s="155"/>
+      <c r="K9" s="155" t="inlineStr">
+        <is>
+          <t>  CONTRIBUTION PERDUE</t>
+        </is>
+      </c>
       <c r="L9" s="157"/>
-      <c r="M9" s="155"/>
+      <c r="M9" s="155" t="inlineStr">
+        <is>
+          <t>  STRUCTURE RÉALLOUÉE</t>
+        </is>
+      </c>
       <c r="N9" s="157"/>
-      <c r="O9" s="158"/>
+      <c r="O9" s="155" t="inlineStr">
+        <is>
+          <t>  BASCULES</t>
+        </is>
+      </c>
       <c r="P9" s="159"/>
-      <c r="Q9" s="158"/>
+      <c r="Q9" s="155" t="inlineStr">
+        <is>
+          <t>  IMPACT EBITDA</t>
+        </is>
+      </c>
       <c r="R9" s="160"/>
     </row>
     <row r="10" spans="3:62" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C10" s="161"/>
+      <c r="C10" s="195">
+        <f>SUMPRODUCT(($C$13:$C$72&lt;&gt;"")*1)</f>
+      </c>
       <c r="D10" s="162"/>
       <c r="E10" s="162"/>
       <c r="F10" s="163"/>
-      <c r="G10" s="161"/>
+      <c r="G10" s="195">
+        <f>SUMPRODUCT(($R$13:$R$72="Fermer")*1)</f>
+      </c>
       <c r="H10" s="163"/>
-      <c r="I10" s="164"/>
+      <c r="I10" s="195">
+        <f>SUMPRODUCT(($R$13:$R$72="Fermer")*1,$H$13:$H$72)</f>
+      </c>
       <c r="J10" s="165"/>
-      <c r="K10" s="166"/>
+      <c r="K10" s="197">
+        <f>-SUMPRODUCT(($R$13:$R$72="Fermer")*1,$L$13:$L$72)</f>
+      </c>
       <c r="L10" s="167"/>
-      <c r="M10" s="168"/>
+      <c r="M10" s="196">
+        <f>SUMPRODUCT(($R$13:$R$72="Fermer")*1,$M$13:$M$72)</f>
+      </c>
       <c r="N10" s="169"/>
-      <c r="O10" s="170"/>
+      <c r="O10" s="195">
+        <f>SUMPRODUCT((LEFT($V$13:$V$72,7)="BASCULE")*1)</f>
+      </c>
       <c r="P10" s="171"/>
-      <c r="Q10" s="170"/>
+      <c r="Q10" s="197">
+        <f>SUM($U$13:$U$72)</f>
+      </c>
       <c r="R10" s="172"/>
     </row>
     <row r="11" spans="3:62" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C11" s="162"/>
+      <c r="C11" s="198" t="inlineStr">
+        <is>
+          <t>au budget 2027, maille campus x programme</t>
+        </is>
+      </c>
       <c r="D11" s="162"/>
       <c r="E11" s="162"/>
       <c r="F11" s="162"/>
-      <c r="G11" s="162"/>
+      <c r="G11" s="198" t="inlineStr">
+        <is>
+          <t>décidées ci-dessous</t>
+        </is>
+      </c>
       <c r="H11" s="162"/>
-      <c r="I11" s="173"/>
+      <c r="I11" s="198" t="inlineStr">
+        <is>
+          <t>étudiants</t>
+        </is>
+      </c>
       <c r="J11" s="173"/>
-      <c r="K11" s="174"/>
+      <c r="K11" s="198" t="inlineStr">
+        <is>
+          <t>ce que la fermeture coûte vraiment</t>
+        </is>
+      </c>
       <c r="L11" s="174"/>
-      <c r="M11" s="175"/>
+      <c r="M11" s="198" t="inlineStr">
+        <is>
+          <t>elle change de porteur</t>
+        </is>
+      </c>
       <c r="N11" s="175"/>
-      <c r="O11" s="176"/>
+      <c r="O11" s="198" t="inlineStr">
+        <is>
+          <t>saines avant, en déficit après</t>
+        </is>
+      </c>
       <c r="P11" s="176"/>
-      <c r="Q11" s="176"/>
+      <c r="Q11" s="198" t="inlineStr">
+        <is>
+          <t>effet sur le groupe</t>
+        </is>
+      </c>
     </row>
     <row r="12" spans="3:62" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C12" s="177" t="s">
-        <v>130</v>
-      </c>
-      <c r="D12" s="177" t="s">
-        <v>131</v>
-      </c>
-      <c r="E12" s="177" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="177" t="s">
-        <v>133</v>
-      </c>
-      <c r="G12" s="177" t="s">
-        <v>134</v>
-      </c>
-      <c r="H12" s="177" t="s">
-        <v>135</v>
-      </c>
-      <c r="I12" s="177" t="s">
-        <v>136</v>
-      </c>
-      <c r="J12" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="K12" s="177" t="s">
-        <v>137</v>
-      </c>
-      <c r="L12" s="177" t="s">
-        <v>138</v>
-      </c>
-      <c r="M12" s="177" t="s">
-        <v>139</v>
-      </c>
-      <c r="N12" s="177" t="s">
-        <v>140</v>
-      </c>
-      <c r="O12" s="177" t="s">
-        <v>141</v>
-      </c>
-      <c r="P12" s="177" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q12" s="177" t="s">
-        <v>143</v>
-      </c>
-      <c r="R12" s="177" t="s">
-        <v>144</v>
-      </c>
-      <c r="S12" s="178" t="s">
-        <v>145</v>
-      </c>
-      <c r="T12" s="178" t="s">
-        <v>146</v>
-      </c>
-      <c r="U12" s="178" t="s">
-        <v>147</v>
-      </c>
-      <c r="V12" s="178" t="s">
-        <v>148</v>
+      <c r="C12" s="177" t="inlineStr">
+        <is>
+          <t>Marque</t>
+        </is>
+      </c>
+      <c r="D12" s="177" t="inlineStr">
+        <is>
+          <t>Campus</t>
+        </is>
+      </c>
+      <c r="E12" s="177" t="inlineStr">
+        <is>
+          <t>Programme</t>
+        </is>
+      </c>
+      <c r="F12" s="177" t="inlineStr">
+        <is>
+          <t>Année</t>
+        </is>
+      </c>
+      <c r="G12" s="177" t="inlineStr">
+        <is>
+          <t>Modalité</t>
+        </is>
+      </c>
+      <c r="H12" s="177" t="inlineStr">
+        <is>
+          <t>Effectif</t>
+        </is>
+      </c>
+      <c r="I12" s="177" t="inlineStr">
+        <is>
+          <t>Sections</t>
+        </is>
+      </c>
+      <c r="J12" s="177" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires</t>
+        </is>
+      </c>
+      <c r="K12" s="177" t="inlineStr">
+        <is>
+          <t>Coût variable</t>
+        </is>
+      </c>
+      <c r="L12" s="177" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="M12" s="177" t="inlineStr">
+        <is>
+          <t>Structure allouée</t>
+        </is>
+      </c>
+      <c r="N12" s="177" t="inlineStr">
+        <is>
+          <t>Coût complet</t>
+        </is>
+      </c>
+      <c r="O12" s="177" t="inlineStr">
+        <is>
+          <t>Marge complète</t>
+        </is>
+      </c>
+      <c r="P12" s="177" t="inlineStr">
+        <is>
+          <t>Point mort</t>
+        </is>
+      </c>
+      <c r="Q12" s="177" t="inlineStr">
+        <is>
+          <t>Marge de sécurité</t>
+        </is>
+      </c>
+      <c r="R12" s="177" t="inlineStr">
+        <is>
+          <t>DÉCISION</t>
+        </is>
+      </c>
+      <c r="S12" s="177" t="inlineStr">
+        <is>
+          <t>Structure après</t>
+        </is>
+      </c>
+      <c r="T12" s="177" t="inlineStr">
+        <is>
+          <t>Marge après</t>
+        </is>
+      </c>
+      <c r="U12" s="177" t="inlineStr">
+        <is>
+          <t>Impact EBITDA</t>
+        </is>
+      </c>
+      <c r="V12" s="177" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
       </c>
       <c r="W12" s="179"/>
       <c r="X12" s="179"/>
@@ -9481,7 +9642,7 @@
       <c r="P13" s="190">
         <v>35</v>
       </c>
-      <c r="Q13" s="190">
+      <c r="Q13" s="199">
         <v>0.227274</v>
       </c>
       <c r="R13" s="191" t="s">
@@ -9552,7 +9713,7 @@
       <c r="P14" s="190">
         <v>34</v>
       </c>
-      <c r="Q14" s="190">
+      <c r="Q14" s="199">
         <v>0.14891099999999999</v>
       </c>
       <c r="R14" s="191" t="s">
@@ -9618,7 +9779,7 @@
       <c r="P15" s="190">
         <v>34</v>
       </c>
-      <c r="Q15" s="190">
+      <c r="Q15" s="199">
         <v>0.12393700000000001</v>
       </c>
       <c r="R15" s="191" t="s">
@@ -9684,7 +9845,7 @@
       <c r="P16" s="190">
         <v>43</v>
       </c>
-      <c r="Q16" s="190">
+      <c r="Q16" s="199">
         <v>0.23305899999999999</v>
       </c>
       <c r="R16" s="191" t="s">
@@ -9750,7 +9911,7 @@
       <c r="P17" s="190">
         <v>41</v>
       </c>
-      <c r="Q17" s="190">
+      <c r="Q17" s="199">
         <v>0.15026800000000001</v>
       </c>
       <c r="R17" s="191" t="s">
@@ -9816,7 +9977,7 @@
       <c r="P18" s="190">
         <v>42</v>
       </c>
-      <c r="Q18" s="190">
+      <c r="Q18" s="199">
         <v>0.13053999999999999</v>
       </c>
       <c r="R18" s="191" t="s">
@@ -9882,7 +10043,7 @@
       <c r="P19" s="190">
         <v>35</v>
       </c>
-      <c r="Q19" s="190">
+      <c r="Q19" s="199">
         <v>0.22755</v>
       </c>
       <c r="R19" s="191" t="s">
@@ -9948,7 +10109,7 @@
       <c r="P20" s="190">
         <v>34</v>
       </c>
-      <c r="Q20" s="190">
+      <c r="Q20" s="199">
         <v>0.14854000000000001</v>
       </c>
       <c r="R20" s="191" t="s">
@@ -10014,7 +10175,7 @@
       <c r="P21" s="190">
         <v>34</v>
       </c>
-      <c r="Q21" s="190">
+      <c r="Q21" s="199">
         <v>0.123555</v>
       </c>
       <c r="R21" s="191" t="s">
@@ -10080,7 +10241,7 @@
       <c r="P22" s="190">
         <v>44</v>
       </c>
-      <c r="Q22" s="190">
+      <c r="Q22" s="199">
         <v>0.20524700000000001</v>
       </c>
       <c r="R22" s="191" t="s">
@@ -10146,7 +10307,7 @@
       <c r="P23" s="190">
         <v>43</v>
       </c>
-      <c r="Q23" s="190">
+      <c r="Q23" s="199">
         <v>0.110931</v>
       </c>
       <c r="R23" s="191" t="s">
@@ -10212,7 +10373,7 @@
       <c r="P24" s="190">
         <v>43</v>
       </c>
-      <c r="Q24" s="190">
+      <c r="Q24" s="199">
         <v>9.0253E-2</v>
       </c>
       <c r="R24" s="191" t="s">
@@ -10278,7 +10439,7 @@
       <c r="P25" s="190">
         <v>39</v>
       </c>
-      <c r="Q25" s="190">
+      <c r="Q25" s="199">
         <v>0.30630200000000002</v>
       </c>
       <c r="R25" s="191" t="s">
@@ -10344,7 +10505,7 @@
       <c r="P26" s="190">
         <v>39</v>
       </c>
-      <c r="Q26" s="190">
+      <c r="Q26" s="199">
         <v>0.22741500000000001</v>
       </c>
       <c r="R26" s="191" t="s">
@@ -10410,7 +10571,7 @@
       <c r="P27" s="190">
         <v>63</v>
       </c>
-      <c r="Q27" s="190">
+      <c r="Q27" s="199">
         <v>0.20177899999999999</v>
       </c>
       <c r="R27" s="191" t="s">
@@ -10476,7 +10637,7 @@
       <c r="P28" s="190">
         <v>61</v>
       </c>
-      <c r="Q28" s="190">
+      <c r="Q28" s="199">
         <v>0.14257400000000001</v>
       </c>
       <c r="R28" s="191" t="s">
@@ -10542,7 +10703,7 @@
       <c r="P29" s="190">
         <v>61</v>
       </c>
-      <c r="Q29" s="190">
+      <c r="Q29" s="199">
         <v>0.12912199999999999</v>
       </c>
       <c r="R29" s="191" t="s">
@@ -10608,7 +10769,7 @@
       <c r="P30" s="190">
         <v>56</v>
       </c>
-      <c r="Q30" s="190">
+      <c r="Q30" s="199">
         <v>0.30466199999999999</v>
       </c>
       <c r="R30" s="191" t="s">
@@ -10674,7 +10835,7 @@
       <c r="P31" s="190">
         <v>54</v>
       </c>
-      <c r="Q31" s="190">
+      <c r="Q31" s="199">
         <v>0.24912100000000001</v>
       </c>
       <c r="R31" s="191" t="s">
@@ -10740,7 +10901,7 @@
       <c r="P32" s="190">
         <v>42</v>
       </c>
-      <c r="Q32" s="190">
+      <c r="Q32" s="199">
         <v>0.19725100000000001</v>
       </c>
       <c r="R32" s="191" t="s">
@@ -10806,7 +10967,7 @@
       <c r="P33" s="190">
         <v>41</v>
       </c>
-      <c r="Q33" s="190">
+      <c r="Q33" s="199">
         <v>0.119368</v>
       </c>
       <c r="R33" s="191" t="s">
@@ -10872,7 +11033,7 @@
       <c r="P34" s="190">
         <v>41</v>
       </c>
-      <c r="Q34" s="190">
+      <c r="Q34" s="199">
         <v>9.7953999999999999E-2</v>
       </c>
       <c r="R34" s="191" t="s">
@@ -10938,7 +11099,7 @@
       <c r="P35" s="190">
         <v>37</v>
       </c>
-      <c r="Q35" s="190">
+      <c r="Q35" s="199">
         <v>0.30224499999999999</v>
       </c>
       <c r="R35" s="191" t="s">
@@ -11004,7 +11165,7 @@
       <c r="P36" s="190">
         <v>37</v>
       </c>
-      <c r="Q36" s="190">
+      <c r="Q36" s="199">
         <v>0.219195</v>
       </c>
       <c r="R36" s="191" t="s">
@@ -11070,7 +11231,7 @@
       <c r="P37" s="190">
         <v>44</v>
       </c>
-      <c r="Q37" s="190">
+      <c r="Q37" s="199">
         <v>0.21480099999999999</v>
       </c>
       <c r="R37" s="191" t="s">
@@ -11137,7 +11298,7 @@
       <c r="P38" s="190">
         <v>44</v>
       </c>
-      <c r="Q38" s="190">
+      <c r="Q38" s="199">
         <v>0.11973300000000001</v>
       </c>
       <c r="R38" s="191" t="s">
@@ -11213,7 +11374,7 @@
       <c r="P39" s="190">
         <v>44</v>
       </c>
-      <c r="Q39" s="190">
+      <c r="Q39" s="199">
         <v>9.9704000000000001E-2</v>
       </c>
       <c r="R39" s="191" t="s">
@@ -11289,7 +11450,7 @@
       <c r="P40" s="190">
         <v>40</v>
       </c>
-      <c r="Q40" s="190">
+      <c r="Q40" s="199">
         <v>0.31340800000000002</v>
       </c>
       <c r="R40" s="191" t="s">
@@ -11365,7 +11526,7 @@
       <c r="P41" s="190">
         <v>39</v>
       </c>
-      <c r="Q41" s="190">
+      <c r="Q41" s="199">
         <v>0.23424300000000001</v>
       </c>
       <c r="R41" s="191" t="s">
@@ -11441,7 +11602,7 @@
       <c r="P42" s="190">
         <v>67</v>
       </c>
-      <c r="Q42" s="190">
+      <c r="Q42" s="199">
         <v>8.2946000000000006E-2</v>
       </c>
       <c r="R42" s="191" t="s">
@@ -11517,7 +11678,7 @@
       <c r="P43" s="190">
         <v>42</v>
       </c>
-      <c r="Q43" s="190">
+      <c r="Q43" s="199">
         <v>0.34946199999999999</v>
       </c>
       <c r="R43" s="191" t="s">
@@ -11593,7 +11754,7 @@
       <c r="P44" s="190">
         <v>42</v>
       </c>
-      <c r="Q44" s="190">
+      <c r="Q44" s="199">
         <v>0.33846999999999999</v>
       </c>
       <c r="R44" s="191" t="s">
@@ -11669,7 +11830,7 @@
       <c r="P45" s="190">
         <v>59</v>
       </c>
-      <c r="Q45" s="190">
+      <c r="Q45" s="199">
         <v>0.20142199999999999</v>
       </c>
       <c r="R45" s="191" t="s">
@@ -11745,7 +11906,7 @@
       <c r="P46" s="190">
         <v>58</v>
       </c>
-      <c r="Q46" s="190">
+      <c r="Q46" s="199">
         <v>0.12241200000000001</v>
       </c>
       <c r="R46" s="191" t="s">
@@ -11821,7 +11982,7 @@
       <c r="P47" s="190">
         <v>43</v>
       </c>
-      <c r="Q47" s="190">
+      <c r="Q47" s="199">
         <v>0.35145799999999999</v>
       </c>
       <c r="R47" s="191" t="s">
@@ -11897,7 +12058,7 @@
       <c r="P48" s="190">
         <v>42</v>
       </c>
-      <c r="Q48" s="190">
+      <c r="Q48" s="199">
         <v>0.28047699999999998</v>
       </c>
       <c r="R48" s="191" t="s">
@@ -11973,7 +12134,7 @@
       <c r="P49" s="190">
         <v>43</v>
       </c>
-      <c r="Q49" s="190">
+      <c r="Q49" s="199">
         <v>0.26688699999999999</v>
       </c>
       <c r="R49" s="191" t="s">
@@ -12049,7 +12210,7 @@
       <c r="P50" s="190">
         <v>59</v>
       </c>
-      <c r="Q50" s="190">
+      <c r="Q50" s="199">
         <v>0.125996</v>
       </c>
       <c r="R50" s="191" t="s">
@@ -12125,7 +12286,7 @@
       <c r="P51" s="190">
         <v>58</v>
       </c>
-      <c r="Q51" s="190">
+      <c r="Q51" s="199">
         <v>2.9203E-2</v>
       </c>
       <c r="R51" s="191" t="s">
@@ -12201,7 +12362,7 @@
       <c r="P52" s="190">
         <v>67</v>
       </c>
-      <c r="Q52" s="190">
+      <c r="Q52" s="199">
         <v>0.21778400000000001</v>
       </c>
       <c r="R52" s="191" t="s">
@@ -12277,7 +12438,7 @@
       <c r="P53" s="190">
         <v>65</v>
       </c>
-      <c r="Q53" s="190">
+      <c r="Q53" s="199">
         <v>0.16036700000000001</v>
       </c>
       <c r="R53" s="191" t="s">
@@ -12353,7 +12514,7 @@
       <c r="P54" s="190">
         <v>65</v>
       </c>
-      <c r="Q54" s="190">
+      <c r="Q54" s="199">
         <v>0.13605200000000001</v>
       </c>
       <c r="R54" s="191" t="s">
@@ -12429,7 +12590,7 @@
       <c r="P55" s="190">
         <v>60</v>
       </c>
-      <c r="Q55" s="190">
+      <c r="Q55" s="199">
         <v>0.31487300000000001</v>
       </c>
       <c r="R55" s="191" t="s">
@@ -12505,7 +12666,7 @@
       <c r="P56" s="190">
         <v>58</v>
       </c>
-      <c r="Q56" s="190">
+      <c r="Q56" s="199">
         <v>0.25181599999999998</v>
       </c>
       <c r="R56" s="191" t="s">
@@ -12581,7 +12742,7 @@
       <c r="P57" s="190">
         <v>35</v>
       </c>
-      <c r="Q57" s="190">
+      <c r="Q57" s="199">
         <v>0.14660899999999999</v>
       </c>
       <c r="R57" s="191" t="s">
@@ -12657,7 +12818,7 @@
       <c r="P58" s="190">
         <v>34</v>
       </c>
-      <c r="Q58" s="190">
+      <c r="Q58" s="199">
         <v>5.1686999999999997E-2</v>
       </c>
       <c r="R58" s="191" t="s">
@@ -12733,7 +12894,7 @@
       <c r="P59" s="190">
         <v>25</v>
       </c>
-      <c r="Q59" s="190">
+      <c r="Q59" s="199">
         <v>0.37934400000000001</v>
       </c>
       <c r="R59" s="191" t="s">
@@ -12809,7 +12970,7 @@
       <c r="P60" s="190">
         <v>25</v>
       </c>
-      <c r="Q60" s="190">
+      <c r="Q60" s="199">
         <v>0.309977</v>
       </c>
       <c r="R60" s="191" t="s">
@@ -12876,7 +13037,7 @@
       <c r="P61" s="190">
         <v>25</v>
       </c>
-      <c r="Q61" s="190">
+      <c r="Q61" s="199">
         <v>0.28802800000000001</v>
       </c>
       <c r="R61" s="191" t="s">
@@ -12943,7 +13104,7 @@
       <c r="P62" s="190">
         <v>32</v>
       </c>
-      <c r="Q62" s="190">
+      <c r="Q62" s="199">
         <v>0.29642200000000002</v>
       </c>
       <c r="R62" s="191" t="s">
@@ -13010,7 +13171,7 @@
       <c r="P63" s="190">
         <v>32</v>
       </c>
-      <c r="Q63" s="190">
+      <c r="Q63" s="199">
         <v>0.31292199999999998</v>
       </c>
       <c r="R63" s="191" t="s">
@@ -13077,7 +13238,7 @@
       <c r="P64" s="190">
         <v>44</v>
       </c>
-      <c r="Q64" s="190">
+      <c r="Q64" s="199">
         <v>0.149117</v>
       </c>
       <c r="R64" s="191" t="s">
@@ -13144,7 +13305,7 @@
       <c r="P65" s="190">
         <v>42</v>
       </c>
-      <c r="Q65" s="190">
+      <c r="Q65" s="199">
         <v>7.9193E-2</v>
       </c>
       <c r="R65" s="191" t="s">
@@ -13211,7 +13372,7 @@
       <c r="P66" s="190">
         <v>33</v>
       </c>
-      <c r="Q66" s="190">
+      <c r="Q66" s="199">
         <v>0.36830600000000002</v>
       </c>
       <c r="R66" s="191" t="s">
@@ -13278,7 +13439,7 @@
       <c r="P67" s="190">
         <v>40</v>
       </c>
-      <c r="Q67" s="190">
+      <c r="Q67" s="199">
         <v>0.102614</v>
       </c>
       <c r="R67" s="191" t="s">
@@ -13345,7 +13506,7 @@
       <c r="P68" s="190">
         <v>39</v>
       </c>
-      <c r="Q68" s="190">
+      <c r="Q68" s="199">
         <v>2.8867E-2</v>
       </c>
       <c r="R68" s="191" t="s">
@@ -13412,7 +13573,7 @@
       <c r="P69" s="190">
         <v>39</v>
       </c>
-      <c r="Q69" s="190">
+      <c r="Q69" s="199">
         <v>6.96E-4</v>
       </c>
       <c r="R69" s="191" t="s">
@@ -13479,7 +13640,7 @@
       <c r="P70" s="190">
         <v>48</v>
       </c>
-      <c r="Q70" s="190">
+      <c r="Q70" s="199">
         <v>8.7919999999999998E-2</v>
       </c>
       <c r="R70" s="191" t="s">
@@ -13546,7 +13707,7 @@
       <c r="P71" s="190">
         <v>45</v>
       </c>
-      <c r="Q71" s="190">
+      <c r="Q71" s="199">
         <v>4.2680999999999997E-2</v>
       </c>
       <c r="R71" s="191" t="s">
@@ -13613,7 +13774,7 @@
       <c r="P72" s="190">
         <v>45</v>
       </c>
-      <c r="Q72" s="190">
+      <c r="Q72" s="199">
         <v>1.9726E-2</v>
       </c>
       <c r="R72" s="191" t="s">
